--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,12 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715215.0279002057</v>
+        <v>715215</v>
       </c>
       <c r="R4" t="n">
-        <v>6411695.781937652</v>
+        <v>6411696</v>
       </c>
       <c r="S4" t="n">
         <v>71</v>
@@ -972,19 +967,9 @@
           <t>1996-06-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1996-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,12 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>96245</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715215.0279002057</v>
+        <v>715215</v>
       </c>
       <c r="R5" t="n">
-        <v>6411695.781937652</v>
+        <v>6411696</v>
       </c>
       <c r="S5" t="n">
         <v>71</v>
@@ -1099,19 +1079,9 @@
           <t>1996-06-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1996-06-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,12 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715215.0279002057</v>
+        <v>715215</v>
       </c>
       <c r="R6" t="n">
-        <v>6411695.781937652</v>
+        <v>6411696</v>
       </c>
       <c r="S6" t="n">
         <v>71</v>
@@ -1226,19 +1191,9 @@
           <t>1996-06-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1996-06-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,12 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715215.0279002057</v>
+        <v>715215</v>
       </c>
       <c r="R7" t="n">
-        <v>6411695.781937652</v>
+        <v>6411696</v>
       </c>
       <c r="S7" t="n">
         <v>71</v>
@@ -1353,19 +1303,9 @@
           <t>1996-06-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1996-06-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,12 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>96359</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715215.0279002057</v>
+        <v>715215</v>
       </c>
       <c r="R8" t="n">
-        <v>6411695.781937652</v>
+        <v>6411696</v>
       </c>
       <c r="S8" t="n">
         <v>71</v>
@@ -1480,19 +1415,9 @@
           <t>1996-06-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1996-06-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,12 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715217.7188153596</v>
+        <v>715218</v>
       </c>
       <c r="R9" t="n">
-        <v>6411495.649257844</v>
+        <v>6411496</v>
       </c>
       <c r="S9" t="n">
         <v>71</v>
@@ -1607,19 +1527,9 @@
           <t>1996-06-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1996-06-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99254</v>
+        <v>99260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98489</v>
+        <v>98495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98581</v>
+        <v>98587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105519</v>
+        <v>105528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98605</v>
+        <v>98611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98495</v>
+        <v>98498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105528</v>
+        <v>105540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98498</v>
+        <v>98501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105540</v>
+        <v>105549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98614</v>
+        <v>98617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98617</v>
+        <v>98618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105552</v>
+        <v>105580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98618</v>
+        <v>98645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98529</v>
+        <v>98535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105580</v>
+        <v>105586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98645</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98535</v>
+        <v>98542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105586</v>
+        <v>105593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98542</v>
+        <v>98546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105593</v>
+        <v>105597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98658</v>
+        <v>98662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98546</v>
+        <v>98553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105597</v>
+        <v>105604</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98556</v>
+        <v>98561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98648</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105607</v>
+        <v>105612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>106585690</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>106585703</v>
       </c>
       <c r="B5" t="n">
-        <v>98561</v>
+        <v>98569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>106585700</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>106585693</v>
       </c>
       <c r="B7" t="n">
-        <v>105612</v>
+        <v>105620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>106585699</v>
       </c>
       <c r="B8" t="n">
-        <v>98677</v>
+        <v>98685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>106585651</v>
       </c>
       <c r="B9" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>95436316</v>
       </c>
       <c r="B2" t="n">
-        <v>96319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715103.6449123289</v>
+        <v>715103</v>
       </c>
       <c r="R2" t="n">
-        <v>6411597.425700898</v>
+        <v>6411598</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95436220</v>
+        <v>106585700</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715087.8043967357</v>
+        <v>715215</v>
       </c>
       <c r="R3" t="n">
-        <v>6411563.465478495</v>
+        <v>6411696</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,60 +854,75 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106585690</v>
+        <v>106585651</v>
       </c>
       <c r="B4" t="n">
-        <v>99336</v>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222322</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Austers 1,95 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715215</v>
+        <v>715218</v>
       </c>
       <c r="R4" t="n">
-        <v>6411696</v>
+        <v>6411496</v>
       </c>
       <c r="S4" t="n">
         <v>71</v>
@@ -983,7 +968,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kärräng, tuvig, dikad.</t>
+          <t>gräsmark, tunn jord</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1011,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106585703</v>
+        <v>106585693</v>
       </c>
       <c r="B5" t="n">
-        <v>98569</v>
+        <v>106140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223572</v>
+        <v>221137</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1123,48 +1108,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106585700</v>
+        <v>95436433</v>
       </c>
       <c r="B6" t="n">
-        <v>98661</v>
+        <v>107061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>221903</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Syd Austers, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715215</v>
+        <v>715670</v>
       </c>
       <c r="R6" t="n">
-        <v>6411696</v>
+        <v>6411322</v>
       </c>
       <c r="S6" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,12 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,57 +1190,42 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106585693</v>
+        <v>106585699</v>
       </c>
       <c r="B7" t="n">
-        <v>105620</v>
+        <v>99145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221137</v>
+        <v>222118</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1347,48 +1317,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106585699</v>
+        <v>95436448</v>
       </c>
       <c r="B8" t="n">
-        <v>98685</v>
+        <v>99803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222118</v>
+        <v>222322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Syd Austers, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715215</v>
+        <v>715252</v>
       </c>
       <c r="R8" t="n">
-        <v>6411696</v>
+        <v>6411800</v>
       </c>
       <c r="S8" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,12 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,75 +1399,60 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106585651</v>
+        <v>106585690</v>
       </c>
       <c r="B9" t="n">
-        <v>98696</v>
+        <v>99803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>222322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Austers 1,95 km S (något till V), Gtl</t>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715218</v>
+        <v>715215</v>
       </c>
       <c r="R9" t="n">
-        <v>6411496</v>
+        <v>6411696</v>
       </c>
       <c r="S9" t="n">
         <v>71</v>
@@ -1543,7 +1498,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>gräsmark, tunn jord</t>
+          <t>Kärräng, tuvig, dikad.</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1564,6 +1519,215 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95436220</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Syd Austers, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>715088</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6411563</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>106585703</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>715215</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S11" t="n">
+        <v>71</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436316</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585700</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436433</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585699</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436448</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585690</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436220</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,8 +1782,25 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>